--- a/data/trans_orig/P55S_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2007</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2007 (tasa de respuesta: 97,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>18198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22803</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>44331</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18792</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>19005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81278</t>
+          <t>80168</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94308</t>
+          <t>93977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134142</t>
+          <t>136162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161354</t>
+          <t>160817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>220913</t>
+          <t>220814</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252512</t>
+          <t>250229</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>27242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11441</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14308</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,62 +1450,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4341</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9705</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,62 +1676,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8963</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2701</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -1984,97 +1984,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>69,55%</t>
         </is>
       </c>
     </row>
@@ -2210,97 +2210,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2177</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>34,59%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>915</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4871</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>42,09%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5049</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36173</t>
+          <t>37231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78366</t>
+          <t>76993</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94694</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111702</t>
+          <t>111202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>141019</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170242</t>
+          <t>170169</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>243502</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>277501</t>
+          <t>276184</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33965</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2012</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2012 (tasa de respuesta: 97,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>22422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45568</t>
+          <t>45965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>33688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61145</t>
+          <t>60601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40776</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66298</t>
+          <t>67075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51360</t>
+          <t>50504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>80195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>81322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101748</t>
+          <t>101679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143117</t>
+          <t>142921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173215</t>
+          <t>175450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232721</t>
+          <t>231285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>271467</t>
+          <t>267635</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>22541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,62 +3957,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4993</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18811</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18855</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -4148,97 +4148,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4491,97 +4491,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1603</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4604,97 +4604,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2215</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5361</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5402</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -4717,97 +4717,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1154</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1603</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11489</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>29322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56361</t>
+          <t>55925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>45924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78481</t>
+          <t>77400</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>21947</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>40796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68056</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50842</t>
+          <t>50780</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80432</t>
+          <t>80960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94784</t>
+          <t>95066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>118364</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>157930</t>
+          <t>158809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191117</t>
+          <t>191210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>262284</t>
+          <t>262720</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>301972</t>
+          <t>302645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>22031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2016</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2016 (tasa de respuesta: 96,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56352</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37725</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>62862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78541</t>
+          <t>78566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131526</t>
+          <t>130591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>159977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>201847</t>
+          <t>199788</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>234065</t>
+          <t>232720</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22451</t>
+          <t>22634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -6429,97 +6429,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5082</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6038</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21334</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44117</t>
+          <t>41605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>17441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>76,41%</t>
         </is>
       </c>
     </row>
@@ -6998,97 +6998,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -7224,97 +7224,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26215</t>
+          <t>26023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58628</t>
+          <t>59190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46339</t>
+          <t>45469</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77914</t>
+          <t>75345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>33425</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85917</t>
+          <t>85574</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103693</t>
+          <t>102806</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>164756</t>
+          <t>161820</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197482</t>
+          <t>196479</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>255990</t>
+          <t>256971</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>294236</t>
+          <t>294292</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13564</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33523</t>
+          <t>33383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37119</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2023</t>
+          <t>Población según el tipo de ayuda que tiene con sus dificultades en las actividades instrumentales de la vida diaria en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>40848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32587</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51421</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31203</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56941</t>
+          <t>57799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76952</t>
+          <t>77149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103191</t>
+          <t>102529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53506</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68235</t>
+          <t>68301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>138253</t>
+          <t>137004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160560</t>
+          <t>159798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>196455</t>
+          <t>195805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>224422</t>
+          <t>222373</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10762</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14746</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>31196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>62202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,68%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>384</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>532</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>37341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56118</t>
+          <t>54945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>55947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79575</t>
+          <t>78761</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>39594</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72087</t>
+          <t>71235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93451</t>
+          <t>92992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98802</t>
+          <t>100789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126686</t>
+          <t>126679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86270</t>
+          <t>85712</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105155</t>
+          <t>104887</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>171178</t>
+          <t>171337</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>196096</t>
+          <t>196895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>263002</t>
+          <t>261876</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>294048</t>
+          <t>293212</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,82%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30899</t>
+          <t>31214</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P55S_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P55S_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23050</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44331</t>
+          <t>44084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>31707</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56295</t>
+          <t>56845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>80886</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93977</t>
+          <t>94099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136162</t>
+          <t>135156</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160817</t>
+          <t>160530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>220814</t>
+          <t>221720</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250229</t>
+          <t>251169</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10932</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,52%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22788</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76993</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93830</t>
+          <t>95517</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142671</t>
+          <t>143405</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>171563</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>242664</t>
+          <t>243818</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>276184</t>
+          <t>276047</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>22373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>46570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>34004</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60601</t>
+          <t>61929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>40618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67075</t>
+          <t>68453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50504</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80195</t>
+          <t>80347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81322</t>
+          <t>81770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101679</t>
+          <t>101661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142921</t>
+          <t>141844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175450</t>
+          <t>173882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>229828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>267635</t>
+          <t>269056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4760</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9329</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22762</t>
+          <t>23247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35422</t>
+          <t>35755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,35%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55925</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45924</t>
+          <t>46516</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77400</t>
+          <t>76341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21947</t>
+          <t>21118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40796</t>
+          <t>39818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66239</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50780</t>
+          <t>53261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80960</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>95066</t>
+          <t>94950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>118364</t>
+          <t>117915</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>158809</t>
+          <t>158900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>191210</t>
+          <t>192788</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>262720</t>
+          <t>264216</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>302645</t>
+          <t>303082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>20491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56104</t>
+          <t>55574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62862</t>
+          <t>62275</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78566</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130591</t>
+          <t>131979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159977</t>
+          <t>160530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>199788</t>
+          <t>200820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232720</t>
+          <t>233263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,23%</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22634</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>21516</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14528</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>40956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41605</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>59561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75345</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33425</t>
+          <t>33079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85574</t>
+          <t>86182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102806</t>
+          <t>102965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>163000</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>196479</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>256971</t>
+          <t>256240</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>294292</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14844</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35393</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>17222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>34842</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24519</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40848</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32816</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51181</t>
+          <t>57350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>32819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66875</t>
+          <t>71238</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57799</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77149</t>
+          <t>83081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>90635</t>
+          <t>96377</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79061</t>
+          <t>84235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>102529</t>
+          <t>108806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -8475,17 +8475,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60579</t>
+          <t>64366</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68301</t>
+          <t>71970</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149361</t>
+          <t>159792</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>137004</t>
+          <t>147007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159798</t>
+          <t>171604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>209941</t>
+          <t>224158</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>195805</t>
+          <t>208266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>222373</t>
+          <t>237771</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,48%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12860</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97656</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>257671</t>
+          <t>276813</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>257671</t>
+          <t>276813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257671</t>
+          <t>276813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>355327</t>
+          <t>380584</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355327</t>
+          <t>380584</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>355327</t>
+          <t>380584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9508</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18505</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>23144</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26406</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>29147</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>23657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32745</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>54343</t>
+          <t>61708</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47735</t>
+          <t>53965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62202</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,85%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>62654</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>62654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54662</t>
+          <t>62654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>97680</t>
+          <t>109976</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97680</t>
+          <t>109976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97680</t>
+          <t>109976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>390</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>401</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>13512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15339</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14988</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>50758</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37341</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54945</t>
+          <t>61358</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>66374</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55947</t>
+          <t>60464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78761</t>
+          <t>85588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>42423</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>82087</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71235</t>
+          <t>75541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>92992</t>
+          <t>99775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>121282</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100789</t>
+          <t>105323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126679</t>
+          <t>135676</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>96081</t>
+          <t>103936</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85712</t>
+          <t>93935</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104887</t>
+          <t>113922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>183542</t>
+          <t>199921</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>171337</t>
+          <t>185146</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>196895</t>
+          <t>213145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>279623</t>
+          <t>303857</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261876</t>
+          <t>286757</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>293212</t>
+          <t>321608</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9826</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17484</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>155794</t>
+          <t>167666</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155794</t>
+          <t>167666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155794</t>
+          <t>167666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>326320</t>
+          <t>355211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326320</t>
+          <t>355211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326320</t>
+          <t>355211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>482113</t>
+          <t>522877</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>482113</t>
+          <t>522877</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482113</t>
+          <t>522877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
